--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0067.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0067.xlsx
@@ -11705,7 +11705,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Test1-Short Kiếm</t>
+          <t>Kiểm tra 1 - Kiếm Ngắn</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11775,7 +11775,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -12055,7 +12055,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12195,7 +12195,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Ultrasonic Judgement</t>
+          <t>Phán Quyết Siêu Âm</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12335,7 +12335,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12475,7 +12475,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12615,7 +12615,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12685,7 +12685,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Originite: Type I</t>
+          <t>Originite: Loại I</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12755,7 +12755,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12965,7 +12965,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Thời Đại Thu Hoạch</t>
+          <t>Ages of Harvest</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13035,7 +13035,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13105,7 +13105,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13175,7 +13175,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Broadblade#41</t>
+          <t>Kiếm Rộng #41</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13245,7 +13245,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13385,7 +13385,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13525,7 +13525,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13665,7 +13665,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13805,7 +13805,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13875,7 +13875,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Suy Tư Về Lòng Thương Xót</t>
+          <t>Thiền định về Lòng Nhân Ái</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13945,7 +13945,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14015,7 +14015,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Beguiling Melody</t>
+          <t>Giai Điệu Quyến Rũ</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14155,7 +14155,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14295,7 +14295,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14435,7 +14435,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14575,7 +14575,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14785,7 +14785,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14855,7 +14855,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Những Truyện Ngụ Ngôn Của Trí Tuệ</t>
+          <t>Truyện Ngụ Ngôn Minh Triết</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14925,7 +14925,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -15065,7 +15065,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15205,7 +15205,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15275,7 +15275,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Khúc Tình Ca Ly Biệt</t>
+          <t>Lãng Mạn Trong Lời Vĩnh Biệt</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15345,7 +15345,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15485,7 +15485,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15625,7 +15625,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15765,7 +15765,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15835,7 +15835,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Celestial Spiral</t>
+          <t>Xoáy Trời Cao</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15905,7 +15905,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -16045,7 +16045,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16115,7 +16115,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Call of the Abyss</t>
+          <t>Tiếng Gọi Vực Sâu</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16185,7 +16185,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16325,7 +16325,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16395,7 +16395,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Ocean's Gift</t>
+          <t>Món Quà Của Đại Dương</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16535,7 +16535,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16675,7 +16675,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16815,7 +16815,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16885,7 +16885,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Waltz in Masquerade</t>
+          <t>Điệu Van-xơ Mặt Nạ</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16955,7 +16955,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Divine Blessing</t>
+          <t>Phước Lành Thần Thánh</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17025,7 +17025,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Blazing Starfire</t>
+          <t>Hỏa Tinh Bùng Cháy</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17095,7 +17095,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Graceful Touch</t>
+          <t>Chạm Nhẹ Ân Sủng</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17165,7 +17165,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Rhetoric</t>
+          <t>Hùng Biện</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17235,7 +17235,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Crimson Phoenix</t>
+          <t>Phượng Hoàng Đỏ Lửa</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17865,7 +17865,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>test weapon</t>
+          <t>Thử nghiệm vũ khí</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17935,7 +17935,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>test weapon</t>
+          <t>Thử nghiệm vũ khí</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18005,7 +18005,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>test weapon</t>
+          <t>Thử nghiệm vũ khí</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18075,7 +18075,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>test weapon</t>
+          <t>Thử nghiệm vũ khí</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18145,7 +18145,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>T4-5Jinzhou+ Series Greatsword</t>
+          <t>Đại Kiếm Loạt T4-5Jinzhou+</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18215,7 +18215,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18355,7 +18355,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18495,7 +18495,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18635,7 +18635,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18705,7 +18705,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Training Kiếm</t>
+          <t>Training Sword</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18775,7 +18775,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18845,7 +18845,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Tyro Kiếm</t>
+          <t>Tyro Sword</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18915,7 +18915,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Kiếm of Night</t>
+          <t>Sword of Night</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19055,7 +19055,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19125,7 +19125,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Ultrasonic Razor</t>
+          <t>Lưỡi Dao Siêu Âm</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19195,7 +19195,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19335,7 +19335,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19405,7 +19405,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19475,7 +19475,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Originite: Type II</t>
+          <t>Originite: Loại II</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19545,7 +19545,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19685,7 +19685,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19755,7 +19755,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19825,7 +19825,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Kiếm#18</t>
+          <t>Thanh Kiếm #18</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19895,7 +19895,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19965,7 +19965,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Kiếm of Voyager</t>
+          <t>Sword of Voyager</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20035,7 +20035,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20175,7 +20175,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20245,7 +20245,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Guardian Kiếm</t>
+          <t>Guardian Sword</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20315,7 +20315,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>test weapon</t>
+          <t>Thử nghiệm vũ khí</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20385,7 +20385,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>test weapon</t>
+          <t>Thử nghiệm vũ khí</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20455,7 +20455,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>test weapon</t>
+          <t>Thử nghiệm vũ khí</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20525,7 +20525,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>test weapon</t>
+          <t>Thử nghiệm vũ khí</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20595,7 +20595,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>T4-5Jinzhou+ series short sword</t>
+          <t>Kiếm ngắn Loạt T4-5Jinzhou+</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20665,7 +20665,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20805,7 +20805,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20945,7 +20945,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21085,7 +21085,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21225,7 +21225,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21365,7 +21365,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21505,7 +21505,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21575,7 +21575,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Ultrasonic Roscoe</t>
+          <t>Súng Ngắn Siêu Âm Roscoe</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21645,7 +21645,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21785,7 +21785,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21855,7 +21855,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Originite: Type III</t>
+          <t>Originite: Loại III</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21925,7 +21925,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21995,7 +21995,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Cadenza</t>
+          <t>Khúc Hoàn Mĩ</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22065,7 +22065,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22135,7 +22135,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22205,7 +22205,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Pistols#26</t>
+          <t>Súng lục #26</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22345,7 +22345,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22485,7 +22485,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22625,7 +22625,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>test weapon</t>
+          <t>Thử nghiệm vũ khí</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22695,7 +22695,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>test weapon</t>
+          <t>Thử nghiệm vũ khí</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22765,7 +22765,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>test weapon</t>
+          <t>Thử nghiệm vũ khí</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22835,7 +22835,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>test weapon</t>
+          <t>Thử nghiệm vũ khí</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22905,7 +22905,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>T4-5Jinzhou+ series pistols</t>
+          <t>Súng ngắn Loạt T4-5Jinzhou+</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22975,7 +22975,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23115,7 +23115,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23255,7 +23255,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23325,7 +23325,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Relativistic Jet</t>
+          <t>Tia Tương Đối</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23395,7 +23395,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23535,7 +23535,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23675,7 +23675,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23815,7 +23815,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23885,7 +23885,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Ultrasonic Rockbreaker</t>
+          <t>Máy Phá Đá Siêu Âm</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23955,7 +23955,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24095,7 +24095,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24165,7 +24165,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Originite: Type IV</t>
+          <t>Originite: Loại IV</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24235,7 +24235,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24375,7 +24375,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24445,7 +24445,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24515,7 +24515,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Gauntlets#21D</t>
+          <t>Bao Tay#21D</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24655,7 +24655,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24795,7 +24795,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24935,7 +24935,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25075,7 +25075,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25215,7 +25215,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25355,7 +25355,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25495,7 +25495,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25635,7 +25635,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25705,7 +25705,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Ultrasonic Matrix</t>
+          <t>Ma Trận Siêu Âm</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25775,7 +25775,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25915,7 +25915,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -26055,7 +26055,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26125,7 +26125,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Originite: Type V</t>
+          <t>Originite: Loại V</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26195,7 +26195,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26335,7 +26335,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26405,7 +26405,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26475,7 +26475,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Rectifier#25</t>
+          <t>Chỉnh Tần #25</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26545,7 +26545,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26685,7 +26685,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26825,7 +26825,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26965,7 +26965,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27105,7 +27105,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>test weapon</t>
+          <t>Thử nghiệm vũ khí</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27175,7 +27175,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>test weapon</t>
+          <t>Thử nghiệm vũ khí</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27245,7 +27245,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>test weapon</t>
+          <t>Thử nghiệm vũ khí</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27315,7 +27315,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>test weapon</t>
+          <t>Thử nghiệm vũ khí</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27385,7 +27385,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Bộ công cụ pháp lý T4-5Jinzhou+</t>
+          <t>Bộ công cụ pháp lý Loạt T4-5Jinzhou+</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27455,7 +27455,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27595,7 +27595,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27665,7 +27665,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Augment</t>
+          <t>Tăng Cường</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27735,7 +27735,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27805,7 +27805,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Forged Dwarf Star</t>
+          <t>Ngôi Sao Lùn Đã Rèn</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27875,7 +27875,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Fusion Accretion</t>
+          <t>Tích Tụ Hợp Nhất</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Projection: Formless Broadblade</t>
+          <t>Hình chiếu: Kiếm Vô Hình</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28085,7 +28085,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Projection: Formless Kiếm</t>
+          <t>Hình chiếu: Kiếm Vô Hình</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28225,7 +28225,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Projection: Formless Pistol</t>
+          <t>Hình chiếu: Súng Vô Hình</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28365,7 +28365,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Projection: Formless Gauntlets</t>
+          <t>Hình chiếu: Găng Tay Vô Hình</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28505,7 +28505,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Projection: Formless Rectifier</t>
+          <t>Hình chiếu: Bộ Chỉnh Lưu Vô Hình</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28645,7 +28645,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Projection: Somnoire Anchor</t>
+          <t>Hình chiếu: Somnoire Anchor</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28785,7 +28785,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Projection - Peach Blossom</t>
+          <t>Hình chiếu - Hoa Đào</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28925,7 +28925,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Projection: Ocean's Gift</t>
+          <t>Hình chiếu: Món Quà Của Đại Dương</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -29345,7 +29345,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Valiance</t>
+          <t>Dũng Khí</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29415,7 +29415,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Valiance</t>
+          <t>Dũng Khí</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29485,7 +29485,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Valiance</t>
+          <t>Dũng Khí</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29555,7 +29555,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Valiance</t>
+          <t>Dũng Khí</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29625,7 +29625,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Valiance</t>
+          <t>Dũng Khí</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29695,7 +29695,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Valiance</t>
+          <t>Dũng Khí</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29765,7 +29765,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Valiance</t>
+          <t>Dũng Khí</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29835,7 +29835,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Valiance</t>
+          <t>Dũng Khí</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29905,7 +29905,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Valiance</t>
+          <t>Dũng Khí</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29975,7 +29975,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Valiance</t>
+          <t>Dũng Khí</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30045,7 +30045,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Persevere</t>
+          <t>Kiên trì lên</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30115,7 +30115,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Valiance</t>
+          <t>Dũng Khí</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30185,7 +30185,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Stormy Resolution</t>
+          <t>Quyết Tâm Trong Bão Tố</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30255,7 +30255,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Stormy Resolution</t>
+          <t>Quyết Tâm Trong Bão Tố</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30325,7 +30325,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Stormy Resolution</t>
+          <t>Quyết Tâm Trong Bão Tố</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30395,7 +30395,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Stormy Resolution</t>
+          <t>Quyết Tâm Trong Bão Tố</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30465,7 +30465,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Stormy Resolution</t>
+          <t>Quyết Tâm Trong Bão Tố</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30535,7 +30535,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Temperance</t>
+          <t>Điều Độ</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30605,7 +30605,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Temperance</t>
+          <t>Điều Độ</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30675,7 +30675,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Temperance</t>
+          <t>Điều Độ</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30745,7 +30745,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Persevere</t>
+          <t>Kiên trì lên</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30815,7 +30815,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Temperance</t>
+          <t>Điều Độ</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30885,7 +30885,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Temperance</t>
+          <t>Điều Độ</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30955,7 +30955,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Vanquish</t>
+          <t>Tiêu diệt</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31025,7 +31025,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Vanquish</t>
+          <t>Tiêu diệt</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31095,7 +31095,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Vanquish</t>
+          <t>Tiêu diệt</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31165,7 +31165,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Vanquish</t>
+          <t>Tiêu diệt</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31235,7 +31235,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Vanquish</t>
+          <t>Tiêu diệt</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31305,7 +31305,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Augment</t>
+          <t>Tăng Cường</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31375,7 +31375,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Persevere</t>
+          <t>Kiên trì lên</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31445,7 +31445,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Augment</t>
+          <t>Tăng Cường</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31515,7 +31515,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Augment</t>
+          <t>Tăng Cường</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31585,7 +31585,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Augment</t>
+          <t>Tăng Cường</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31655,7 +31655,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Augment</t>
+          <t>Tăng Cường</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31725,7 +31725,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Veteran</t>
+          <t>Lão luyện</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31795,7 +31795,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Veteran</t>
+          <t>Lão luyện</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31865,7 +31865,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Veteran</t>
+          <t>Lão luyện</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31935,7 +31935,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Veteran</t>
+          <t>Lão luyện</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32005,7 +32005,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Veteran</t>
+          <t>Lão luyện</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32075,7 +32075,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Persevere</t>
+          <t>Kiên trì lên</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32145,7 +32145,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Daybreak</t>
+          <t>Bình Minh</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32215,7 +32215,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Daybreak</t>
+          <t>Bình Minh</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32285,7 +32285,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Daybreak</t>
+          <t>Bình Minh</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32355,7 +32355,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Daybreak</t>
+          <t>Bình Minh</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32425,7 +32425,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Daybreak</t>
+          <t>Bình Minh</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32495,7 +32495,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Dawnbringer</t>
+          <t>Kẻ Mang Bình Minh</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32565,7 +32565,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Dawnbringer</t>
+          <t>Kẻ Mang Bình Minh</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32635,7 +32635,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Dawnbringer</t>
+          <t>Kẻ Mang Bình Minh</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32705,7 +32705,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Persevere</t>
+          <t>Kiên trì lên</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32775,7 +32775,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Dawnbringer</t>
+          <t>Kẻ Mang Bình Minh</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32845,7 +32845,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Dawnbringer</t>
+          <t>Kẻ Mang Bình Minh</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32915,7 +32915,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Battlebound</t>
+          <t>Sẵn sàng chiến đấu</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32985,7 +32985,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Battlebound</t>
+          <t>Sẵn sàng chiến đấu</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33055,7 +33055,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Battlebound</t>
+          <t>Sẵn sàng chiến đấu</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33125,7 +33125,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Battlebound</t>
+          <t>Sẵn sàng chiến đấu</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33195,7 +33195,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Battlebound</t>
+          <t>Sẵn sàng chiến đấu</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33265,7 +33265,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Unyielding</t>
+          <t>Bất Khuất</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33335,7 +33335,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Unyielding</t>
+          <t>Bất Khuất</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33405,7 +33405,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Persevere</t>
+          <t>Kiên trì lên</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33475,7 +33475,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Unyielding</t>
+          <t>Bất Khuất</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33545,7 +33545,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Unyielding</t>
+          <t>Bất Khuất</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33615,7 +33615,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Unyielding</t>
+          <t>Bất Khuất</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33685,7 +33685,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Loyalty</t>
+          <t>Lòng Trung Thành</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33755,7 +33755,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Loyalty</t>
+          <t>Lòng Trung Thành</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33825,7 +33825,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Loyalty</t>
+          <t>Lòng Trung Thành</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33895,7 +33895,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Loyalty</t>
+          <t>Lòng Trung Thành</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33965,7 +33965,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Loyalty</t>
+          <t>Lòng Trung Thành</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34035,7 +34035,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Camaraderie</t>
+          <t>Tình Đồng Đội</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34105,7 +34105,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Camaraderie</t>
+          <t>Tình Đồng Đội</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34175,7 +34175,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Persevere</t>
+          <t>Kiên trì lên</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34245,7 +34245,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Camaraderie</t>
+          <t>Tình Đồng Đội</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34315,7 +34315,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Camaraderie</t>
+          <t>Tình Đồng Đội</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34385,7 +34385,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Camaraderie</t>
+          <t>Tình Đồng Đội</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34455,7 +34455,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Guardian</t>
+          <t>Người Bảo Vệ</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34525,7 +34525,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Guardian</t>
+          <t>Người Bảo Vệ</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34595,7 +34595,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Guardian</t>
+          <t>Người Bảo Vệ</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34665,7 +34665,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Guardian</t>
+          <t>Người Bảo Vệ</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34735,7 +34735,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Guardian</t>
+          <t>Người Bảo Vệ</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34805,7 +34805,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Undying Lonelamp</t>
+          <t>Ngọn Đèn Cô Đơn Bất Tử</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34875,7 +34875,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Persevere</t>
+          <t>Kiên trì lên</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34945,7 +34945,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Unmatched Blade</t>
+          <t>Lưỡi Kiếm Vô Đối</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35015,7 +35015,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Unswerving Hymn</t>
+          <t>Khúc Ca Bất Khuất</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35085,7 +35085,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Unlimited Ambition</t>
+          <t>Tham vọng vô biên</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35155,7 +35155,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Unrestrained Breeze</t>
+          <t>Cơn Gió Phóng Khoáng</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35225,7 +35225,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Persevere</t>
+          <t>Kiên trì lên</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35295,7 +35295,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Persevere</t>
+          <t>Kiên trì lên</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35365,7 +35365,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Persevere</t>
+          <t>Kiên trì lên</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35435,7 +35435,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Persevere</t>
+          <t>Kiên trì lên</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35505,7 +35505,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Swordsworn</t>
+          <t>Kiếm Thệ</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
